--- a/data/trans_dic/P1410-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1410-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,23</t>
+          <t>3,11; 7,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,41</t>
+          <t>1,34; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,36</t>
+          <t>1,57; 5,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,63</t>
+          <t>3,91; 7,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,58</t>
+          <t>0,37; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,44</t>
+          <t>2,22; 6,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,32</t>
+          <t>1,78; 4,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,95</t>
+          <t>2,33; 5,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,69</t>
+          <t>0,91; 2,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,99</t>
+          <t>2,27; 5,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,05</t>
+          <t>3,13; 5,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,66</t>
+          <t>1,89; 5,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,08</t>
+          <t>1,25; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,86</t>
+          <t>1,96; 5,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,1</t>
+          <t>2,83; 5,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,18</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,11</t>
+          <t>0,29; 3,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,44</t>
+          <t>0,6; 3,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,4</t>
+          <t>0,52; 2,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,72</t>
+          <t>1,49; 3,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,4</t>
+          <t>1,1; 3,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,88</t>
+          <t>1,6; 4,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,88</t>
+          <t>2,0; 3,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,83</t>
+          <t>3,32; 6,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,99</t>
+          <t>3,3; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,44</t>
+          <t>2,89; 6,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,25</t>
+          <t>4,49; 8,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,3</t>
+          <t>0,56; 5,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,76</t>
+          <t>1,75; 6,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,41</t>
+          <t>3,69; 12,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 12,04</t>
+          <t>3,39; 12,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,69</t>
+          <t>2,78; 5,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,05</t>
+          <t>3,21; 6,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,99</t>
+          <t>3,59; 7,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,86</t>
+          <t>4,79; 8,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,2</t>
+          <t>4,5; 7,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,73</t>
+          <t>3,32; 5,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,79</t>
+          <t>3,27; 5,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,64</t>
+          <t>4,84; 7,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,18</t>
+          <t>2,3; 5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,33</t>
+          <t>1,21; 3,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,1</t>
+          <t>1,75; 4,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,01</t>
+          <t>1,77; 3,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 5,91</t>
+          <t>4,03; 5,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,58</t>
+          <t>2,63; 4,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,73</t>
+          <t>2,93; 4,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,16</t>
+          <t>3,73; 5,49</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,78</t>
+          <t>3,1; 7,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,7</t>
+          <t>2,97; 6,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,16</t>
+          <t>2,97; 6,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,2</t>
+          <t>4,47; 8,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,06</t>
+          <t>3,35; 7,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,86</t>
+          <t>5,0; 8,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,01</t>
+          <t>2,91; 6,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,87</t>
+          <t>5,08; 7,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,7</t>
+          <t>3,77; 6,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,5</t>
+          <t>4,57; 7,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,58</t>
+          <t>3,35; 5,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,21</t>
+          <t>5,24; 7,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,96</t>
+          <t>0,36; 5,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 10,06</t>
+          <t>0,22; 9,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,04</t>
+          <t>3,78; 6,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,46</t>
+          <t>4,62; 7,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,74</t>
+          <t>5,05; 8,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,47</t>
+          <t>5,55; 8,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,01</t>
+          <t>3,09; 5,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,42</t>
+          <t>3,92; 6,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,84</t>
+          <t>4,2; 6,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,54</t>
+          <t>4,65; 7,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 5,38</t>
+          <t>3,9; 5,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,6</t>
+          <t>3,2; 4,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,41</t>
+          <t>3,14; 4,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,97</t>
+          <t>4,67; 6,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,45</t>
+          <t>3,12; 4,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,86</t>
+          <t>3,49; 4,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,32</t>
+          <t>3,84; 5,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,75</t>
+          <t>3,91; 5,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,69</t>
+          <t>3,7; 4,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,49</t>
+          <t>3,54; 4,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 4,64</t>
+          <t>3,66; 4,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 5,18</t>
+          <t>4,51; 5,39</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>43074</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14500; 34230</t>
+          <t>14749; 33207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5875; 19267</t>
+          <t>5865; 19235</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6823; 22999</t>
+          <t>6716; 22972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16778; 33470</t>
+          <t>21506; 40613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1143; 10980</t>
+          <t>1131; 11123</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5860</t>
+          <t>0; 5608</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7514; 22357</t>
+          <t>7717; 22457</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7665; 19329</t>
+          <t>8674; 21320</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17664; 38628</t>
+          <t>18167; 39555</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6950; 20244</t>
+          <t>6845; 20775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17392; 38740</t>
+          <t>17655; 39589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27928; 48063</t>
+          <t>32533; 54545</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>25331</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6728; 20765</t>
+          <t>6920; 20362</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5508; 21258</t>
+          <t>5215; 20673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6848; 22108</t>
+          <t>7384; 21260</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12457; 27579</t>
+          <t>13659; 28835</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2118; 15555</t>
+          <t>2330; 13832</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>982; 10526</t>
+          <t>967; 10727</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2400; 12789</t>
+          <t>2251; 12532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2249; 9169</t>
+          <t>2212; 9751</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11077; 27498</t>
+          <t>11006; 27931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8825; 25712</t>
+          <t>8339; 25200</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11469; 29090</t>
+          <t>12015; 31212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16706; 32361</t>
+          <t>18088; 34698</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>41539</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17658; 37041</t>
+          <t>17983; 36513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21407; 44022</t>
+          <t>20750; 42490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15079; 33598</t>
+          <t>15102; 33014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9695; 48389</t>
+          <t>21134; 40780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>940; 8900</t>
+          <t>939; 8925</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5075; 17574</t>
+          <t>4555; 17380</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6310; 22278</t>
+          <t>6133; 21096</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6060; 20092</t>
+          <t>6360; 23442</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19705; 40418</t>
+          <t>19750; 39924</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29208; 53829</t>
+          <t>28563; 53539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24511; 48094</t>
+          <t>24698; 48365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14786; 57235</t>
+          <t>31532; 55352</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84442</t>
+          <t>89878</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56035; 89181</t>
+          <t>55754; 87924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37323; 66380</t>
+          <t>38426; 68707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39142; 66537</t>
+          <t>37605; 65547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51190; 78919</t>
+          <t>54681; 84410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16510; 36966</t>
+          <t>16403; 36326</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10056; 25468</t>
+          <t>9278; 25329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14099; 33828</t>
+          <t>14420; 34530</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9019; 29470</t>
+          <t>15244; 29379</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77887; 115334</t>
+          <t>78632; 115100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52294; 88021</t>
+          <t>50537; 85906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57594; 93532</t>
+          <t>57976; 91942</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61696; 103758</t>
+          <t>74296; 109218</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>34646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>52311</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>86957</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10867; 27281</t>
+          <t>10858; 27489</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15029; 34223</t>
+          <t>15187; 34626</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17527; 38220</t>
+          <t>18427; 37643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24103; 43613</t>
+          <t>25350; 47033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18651; 40131</t>
+          <t>19071; 40860</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39397; 67390</t>
+          <t>38017; 65828</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22365; 44339</t>
+          <t>21495; 44534</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33972; 57572</t>
+          <t>42075; 63676</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35006; 61593</t>
+          <t>34637; 62114</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58906; 95258</t>
+          <t>58040; 92045</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45591; 75866</t>
+          <t>45476; 74368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61754; 94643</t>
+          <t>73110; 102041</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>52968</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>62406</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>970; 13236</t>
+          <t>963; 13493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5933</t>
+          <t>0; 5977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>517; 24191</t>
+          <t>517; 23701</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46186; 75440</t>
+          <t>47143; 76032</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51016; 82700</t>
+          <t>51215; 82707</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57464; 94597</t>
+          <t>54666; 91034</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>43113; 64408</t>
+          <t>46791; 70566</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46238; 77437</t>
+          <t>47842; 77722</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53805; 88294</t>
+          <t>53892; 87393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56708; 93648</t>
+          <t>57483; 94754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46318; 75489</t>
+          <t>50265; 77807</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173535</t>
+          <t>186849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>146950</t>
+          <t>162337</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>320485</t>
+          <t>349186</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>129367; 175840</t>
+          <t>127597; 174915</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>111966; 157398</t>
+          <t>109427; 154934</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106371; 149414</t>
+          <t>106291; 150464</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137503; 201341</t>
+          <t>160647; 211193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106668; 150257</t>
+          <t>105408; 151712</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>124063; 172280</t>
+          <t>123751; 171396</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>132664; 187778</t>
+          <t>135599; 186003</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>120652; 169500</t>
+          <t>142071; 184797</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>244451; 311527</t>
+          <t>246206; 310173</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247688; 313079</t>
+          <t>246954; 314144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>253321; 321169</t>
+          <t>253264; 321884</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>276997; 360007</t>
+          <t>318539; 381353</t>
         </is>
       </c>
     </row>
